--- a/rapporter_2025/Kostra 24 - Fylkesveg med støyskjerm og voll.xlsx
+++ b/rapporter_2025/Kostra 24 - Fylkesveg med støyskjerm og voll.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andryg\Documents\NVDB-Skripting\src\arb_kostrarapportering_2025\rapporter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF75BCAF-B94A-49B6-8C5E-9169A7C9A907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD1059AB-2588-4CC6-AAC0-6EF928EEBB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42165" yWindow="1815" windowWidth="23445" windowHeight="18975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="46650" yWindow="1905" windowWidth="27480" windowHeight="15795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fv med støyskjerm" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t>Fylke</t>
   </si>
@@ -35,12 +35,6 @@
   </si>
   <si>
     <t>Filter</t>
-  </si>
-  <si>
-    <t>trafikantgruppe</t>
-  </si>
-  <si>
-    <t>K</t>
   </si>
   <si>
     <t>tidspunkt</t>
@@ -433,7 +427,7 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="28.85546875" customWidth="1"/>
+    <col min="1" max="3" width="24.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -452,10 +446,10 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>50717</v>
+        <v>55360</v>
       </c>
       <c r="C2">
-        <v>882</v>
+        <v>957</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -463,10 +457,10 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>6508</v>
+        <v>6792</v>
       </c>
       <c r="C3">
-        <v>160</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -474,10 +468,10 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>2192</v>
+        <v>2438</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -485,10 +479,10 @@
         <v>31</v>
       </c>
       <c r="B5">
-        <v>16466</v>
+        <v>15163</v>
       </c>
       <c r="C5">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -496,10 +490,10 @@
         <v>32</v>
       </c>
       <c r="B6">
-        <v>58684</v>
+        <v>66106</v>
       </c>
       <c r="C6">
-        <v>718</v>
+        <v>862</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -507,10 +501,10 @@
         <v>33</v>
       </c>
       <c r="B7">
-        <v>19293</v>
+        <v>19755</v>
       </c>
       <c r="C7">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -518,10 +512,10 @@
         <v>34</v>
       </c>
       <c r="B8">
-        <v>38653</v>
+        <v>39447</v>
       </c>
       <c r="C8">
-        <v>481</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -529,7 +523,7 @@
         <v>39</v>
       </c>
       <c r="B9">
-        <v>29719</v>
+        <v>29533</v>
       </c>
       <c r="C9">
         <v>367</v>
@@ -540,10 +534,10 @@
         <v>40</v>
       </c>
       <c r="B10">
-        <v>13691</v>
+        <v>14744</v>
       </c>
       <c r="C10">
-        <v>207</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -551,10 +545,10 @@
         <v>42</v>
       </c>
       <c r="B11">
-        <v>26778</v>
+        <v>27018</v>
       </c>
       <c r="C11">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -562,10 +556,10 @@
         <v>46</v>
       </c>
       <c r="B12">
-        <v>15942</v>
+        <v>17374</v>
       </c>
       <c r="C12">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -573,10 +567,10 @@
         <v>50</v>
       </c>
       <c r="B13">
-        <v>28174</v>
+        <v>29180</v>
       </c>
       <c r="C13">
-        <v>512</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -584,10 +578,10 @@
         <v>55</v>
       </c>
       <c r="B14">
-        <v>4681</v>
+        <v>5434</v>
       </c>
       <c r="C14">
-        <v>69</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -611,7 +605,7 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="28.85546875" customWidth="1"/>
+    <col min="1" max="3" width="25.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -630,10 +624,10 @@
         <v>11</v>
       </c>
       <c r="B2">
-        <v>9831</v>
+        <v>10343</v>
       </c>
       <c r="C2">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -641,10 +635,10 @@
         <v>15</v>
       </c>
       <c r="B3">
-        <v>6091</v>
+        <v>6111</v>
       </c>
       <c r="C3">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -652,10 +646,10 @@
         <v>18</v>
       </c>
       <c r="B4">
-        <v>2928</v>
+        <v>2973</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -674,10 +668,10 @@
         <v>32</v>
       </c>
       <c r="B6">
-        <v>7229</v>
+        <v>7297</v>
       </c>
       <c r="C6">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -685,10 +679,10 @@
         <v>33</v>
       </c>
       <c r="B7">
-        <v>11116</v>
+        <v>11313</v>
       </c>
       <c r="C7">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -696,10 +690,10 @@
         <v>34</v>
       </c>
       <c r="B8">
-        <v>12350</v>
+        <v>12930</v>
       </c>
       <c r="C8">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -707,7 +701,7 @@
         <v>39</v>
       </c>
       <c r="B9">
-        <v>12030</v>
+        <v>12029</v>
       </c>
       <c r="C9">
         <v>133</v>
@@ -740,10 +734,10 @@
         <v>46</v>
       </c>
       <c r="B12">
-        <v>3616</v>
+        <v>3757</v>
       </c>
       <c r="C12">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -751,10 +745,10 @@
         <v>50</v>
       </c>
       <c r="B13">
-        <v>16411</v>
+        <v>16934</v>
       </c>
       <c r="C13">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -775,10 +769,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -817,14 +811,6 @@
       </c>
       <c r="B5" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -834,10 +820,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -867,7 +853,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -875,15 +861,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
